--- a/data/AWS_SAA_重要キーワード集.xlsx
+++ b/data/AWS_SAA_重要キーワード集.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分野別集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$173</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'キーワード一覧'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="21" min="1" max="1"/>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="D61" s="35" t="inlineStr">
         <is>
-          <t>改ざん不可能な台帳データベース(サービス終了予定のため最新の出題状況を確認)</t>
+          <t>改ざん不可能で、変更履歴(ジャーナル)を暗号技術で検証できる台帳データベース。2025年7月31日にサービス終了</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>変更履歴の検証可能性が必要な場合</t>
+          <t>変更履歴の検証可能性が必要な場合(終了後の移行先としてはAurora PostgreSQLなどが案内されている)</t>
         </is>
       </c>
       <c r="F61" s="38" t="inlineStr">
@@ -5663,15 +5663,294 @@
       </c>
       <c r="G164" s="39" t="n"/>
     </row>
+    <row r="165" ht="29.85" customHeight="1" s="22">
+      <c r="A165" s="34" t="n">
+        <v>161</v>
+      </c>
+      <c r="B165" s="35" t="inlineStr">
+        <is>
+          <t>ストレージ</t>
+        </is>
+      </c>
+      <c r="C165" s="36" t="inlineStr">
+        <is>
+          <t>S3 Glacier Flexible Retrieval</t>
+        </is>
+      </c>
+      <c r="D165" s="35" t="inlineStr">
+        <is>
+          <t>低コストのアーカイブ用クラス(以前の名称はS3 Glacier)。取り出しは迅速(1〜5分)/標準(3〜5時間)/大容量(5〜12時間)から選ぶ。最低保存期間90日</t>
+        </is>
+      </c>
+      <c r="E165" s="37" t="inlineStr">
+        <is>
+          <t>年に1〜2回程度アクセスし、数分〜数時間の取り出し待ちを許容できるバックアップ・アーカイブ</t>
+        </is>
+      </c>
+      <c r="F165" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G165" s="39" t="n"/>
+    </row>
+    <row r="166" ht="29.85" customHeight="1" s="22">
+      <c r="A166" s="34" t="n">
+        <v>162</v>
+      </c>
+      <c r="B166" s="35" t="inlineStr">
+        <is>
+          <t>ストレージ</t>
+        </is>
+      </c>
+      <c r="C166" s="36" t="inlineStr">
+        <is>
+          <t>S3 Glacier Instant Retrieval</t>
+        </is>
+      </c>
+      <c r="D166" s="35" t="inlineStr">
+        <is>
+          <t>アーカイブ向けの低コストなクラスだが、取り出しはStandardと同じミリ秒単位。最低保存期間90日</t>
+        </is>
+      </c>
+      <c r="E166" s="37" t="inlineStr">
+        <is>
+          <t>四半期に1回程度しかアクセスしないが、必要なときは即時に取り出したいデータ(医療画像・ニュース素材など)</t>
+        </is>
+      </c>
+      <c r="F166" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G166" s="39" t="n"/>
+    </row>
+    <row r="167" ht="29.85" customHeight="1" s="22">
+      <c r="A167" s="34" t="n">
+        <v>163</v>
+      </c>
+      <c r="B167" s="35" t="inlineStr">
+        <is>
+          <t>ストレージ</t>
+        </is>
+      </c>
+      <c r="C167" s="36" t="inlineStr">
+        <is>
+          <t>Amazon FSx for NetApp ONTAP</t>
+        </is>
+      </c>
+      <c r="D167" s="35" t="inlineStr">
+        <is>
+          <t>NFS・SMB・iSCSIのマルチプロトコルに対応したフルマネージドファイルシステム。LinuxとWindowsの両方からアクセスでき、NetAppのスナップショットやレプリケーション機能をそのまま使える</t>
+        </is>
+      </c>
+      <c r="E167" s="37" t="inlineStr">
+        <is>
+          <t>オンプレミスのNetApp環境をそのまま移行したい・LinuxとWindowsで同じデータを共有したい</t>
+        </is>
+      </c>
+      <c r="F167" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G167" s="39" t="n"/>
+    </row>
+    <row r="168" ht="29.85" customHeight="1" s="22">
+      <c r="A168" s="34" t="n">
+        <v>164</v>
+      </c>
+      <c r="B168" s="35" t="inlineStr">
+        <is>
+          <t>ストレージ</t>
+        </is>
+      </c>
+      <c r="C168" s="36" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS</t>
+        </is>
+      </c>
+      <c r="D168" s="35" t="inlineStr">
+        <is>
+          <t>ZFSベースのフルマネージドファイルシステム。NFSでアクセスし、スナップショットやクローンを使える</t>
+        </is>
+      </c>
+      <c r="E168" s="37" t="inlineStr">
+        <is>
+          <t>オンプレミスのZFSベースのファイルサーバーをアプリを変えずに移行したい</t>
+        </is>
+      </c>
+      <c r="F168" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G168" s="39" t="n"/>
+    </row>
+    <row r="169" ht="29.85" customHeight="1" s="22">
+      <c r="A169" s="34" t="n">
+        <v>165</v>
+      </c>
+      <c r="B169" s="35" t="inlineStr">
+        <is>
+          <t>データベース</t>
+        </is>
+      </c>
+      <c r="C169" s="36" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom</t>
+        </is>
+      </c>
+      <c r="D169" s="35" t="inlineStr">
+        <is>
+          <t>OSやDBエンジンの基盤にアクセスできるRDS(Oracle・SQL Serverが対象)。自動バックアップなどRDSの管理機能を保ちつつ、OSレベルのカスタマイズや独自パッチの適用ができる</t>
+        </is>
+      </c>
+      <c r="E169" s="37" t="inlineStr">
+        <is>
+          <t>パッケージアプリの要件でDBサーバーのOSへのアクセス・カスタマイズが必要だが、マネージドの利点も残したい</t>
+        </is>
+      </c>
+      <c r="F169" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G169" s="39" t="n"/>
+    </row>
+    <row r="170" ht="29.85" customHeight="1" s="22">
+      <c r="A170" s="34" t="n">
+        <v>166</v>
+      </c>
+      <c r="B170" s="35" t="inlineStr">
+        <is>
+          <t>データベース</t>
+        </is>
+      </c>
+      <c r="C170" s="36" t="inlineStr">
+        <is>
+          <t>Amazon RDS on Outposts</t>
+        </is>
+      </c>
+      <c r="D170" s="35" t="inlineStr">
+        <is>
+          <t>AWS Outpostsを使い、オンプレミス(自社データセンターなど)でRDSのマネージドDBを実行する</t>
+        </is>
+      </c>
+      <c r="E170" s="37" t="inlineStr">
+        <is>
+          <t>データをオンプレミスに置く必要がある(データ所在地要件)・オンプレのアプリから超低レイテンシでDBを使いたい</t>
+        </is>
+      </c>
+      <c r="F170" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G170" s="39" t="n"/>
+    </row>
+    <row r="171" ht="29.85" customHeight="1" s="22">
+      <c r="A171" s="34" t="n">
+        <v>167</v>
+      </c>
+      <c r="B171" s="35" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="C171" s="36" t="inlineStr">
+        <is>
+          <t>Amazon CloudSearch</t>
+        </is>
+      </c>
+      <c r="D171" s="35" t="inlineStr">
+        <is>
+          <t>Webサイトやアプリ向けの検索機能をシンプルに構築できるマネージド型の検索サービス。新規の利用は受け付けておらず、OpenSearch Serviceへの移行が推奨されている</t>
+        </is>
+      </c>
+      <c r="E171" s="37" t="inlineStr">
+        <is>
+          <t>試験ではほぼ出題されない。検索・ログ分析の要件はOpenSearch Serviceを選ぶ</t>
+        </is>
+      </c>
+      <c r="F171" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G171" s="39" t="n"/>
+    </row>
+    <row r="172" ht="29.85" customHeight="1" s="22">
+      <c r="A172" s="34" t="n">
+        <v>168</v>
+      </c>
+      <c r="B172" s="35" t="inlineStr">
+        <is>
+          <t>ネットワーク</t>
+        </is>
+      </c>
+      <c r="C172" s="36" t="inlineStr">
+        <is>
+          <t>AWS Client VPN</t>
+        </is>
+      </c>
+      <c r="D172" s="35" t="inlineStr">
+        <is>
+          <t>OpenVPNベースのクライアントソフトを使い、個々のユーザーの端末からAWSやオンプレミスのネットワークへ安全に接続するマネージドVPN</t>
+        </is>
+      </c>
+      <c r="E172" s="37" t="inlineStr">
+        <is>
+          <t>リモートワークの社員がPCから社内ネットワーク・VPCへ安全にアクセスしたい(拠点間の接続はSite-to-Site VPN)</t>
+        </is>
+      </c>
+      <c r="F172" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G172" s="39" t="n"/>
+    </row>
+    <row r="173" ht="29.85" customHeight="1" s="22">
+      <c r="A173" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="B173" s="35" t="inlineStr">
+        <is>
+          <t>ネットワーク</t>
+        </is>
+      </c>
+      <c r="C173" s="36" t="inlineStr">
+        <is>
+          <t>AWS Cloud WAN</t>
+        </is>
+      </c>
+      <c r="D173" s="35" t="inlineStr">
+        <is>
+          <t>複数リージョン・多数のVPC・オンプレミス拠点をつなぐグローバルなネットワークを、中央のポリシーで一元的に構築・管理するサービス</t>
+        </is>
+      </c>
+      <c r="E173" s="37" t="inlineStr">
+        <is>
+          <t>複数リージョンにまたがる大規模なグローバルネットワークをまとめて管理したい</t>
+        </is>
+      </c>
+      <c r="F173" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G173" s="39" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G164"/>
-  <conditionalFormatting sqref="A5:G164">
+  <autoFilter ref="A4:G173"/>
+  <conditionalFormatting sqref="A5:G173">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>$F5="★★★"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"◎ 説明できる,○ なんとなく,△ 要復習"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5750,23 +6029,23 @@
         </is>
       </c>
       <c r="B4" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A4)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A4)</f>
         <v/>
       </c>
       <c r="C4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A4,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A4,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A4,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A4,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G4" s="44">
@@ -5781,23 +6060,23 @@
         </is>
       </c>
       <c r="B5" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A5)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A5)</f>
         <v/>
       </c>
       <c r="C5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A5,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A5,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A5,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A5,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G5" s="44">
@@ -5812,23 +6091,23 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A6)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A6)</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A6,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A6,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A6,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A6,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G6" s="44">
@@ -5843,23 +6122,23 @@
         </is>
       </c>
       <c r="B7" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A7)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A7)</f>
         <v/>
       </c>
       <c r="C7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A7,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A7,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A7,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A7,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G7" s="44">
@@ -5874,23 +6153,23 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A8)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A8)</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A8,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A8,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A8,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A8,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G8" s="44">
@@ -5905,23 +6184,23 @@
         </is>
       </c>
       <c r="B9" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A9)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A9)</f>
         <v/>
       </c>
       <c r="C9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A9,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A9,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A9,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A9,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G9" s="44">
@@ -5936,23 +6215,23 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A10)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A10)</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A10,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A10,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A10,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A10,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G10" s="44">
@@ -5967,23 +6246,23 @@
         </is>
       </c>
       <c r="B11" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A11)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A11)</f>
         <v/>
       </c>
       <c r="C11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A11,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A11,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A11,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A11,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G11" s="44">
@@ -5998,23 +6277,23 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A12)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A12)</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A12,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A12,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A12,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A12,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G12" s="44">
@@ -6029,23 +6308,23 @@
         </is>
       </c>
       <c r="B13" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A13)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A13)</f>
         <v/>
       </c>
       <c r="C13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A13,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A13,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A13,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A13,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G13" s="44">
@@ -6060,23 +6339,23 @@
         </is>
       </c>
       <c r="B14" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A14)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A14)</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A14,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A14,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A14,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A14,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G14" s="44">
@@ -6091,23 +6370,23 @@
         </is>
       </c>
       <c r="B15" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$164,A15)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A15)</f>
         <v/>
       </c>
       <c r="C15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A15,キーワード一覧!$F$5:$F$164,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$F$5:$F$173,"★★★")</f>
         <v/>
       </c>
       <c r="D15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A15,キーワード一覧!$G$5:$G$164,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$G$5:$G$173,"◎*")</f>
         <v/>
       </c>
       <c r="E15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A15,キーワード一覧!$G$5:$G$164,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$G$5:$G$173,"○*")</f>
         <v/>
       </c>
       <c r="F15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$164,A15,キーワード一覧!$G$5:$G$164,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$G$5:$G$173,"△*")</f>
         <v/>
       </c>
       <c r="G15" s="44">

--- a/data/AWS_SAA_重要キーワード集.xlsx
+++ b/data/AWS_SAA_重要キーワード集.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分野別集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$176</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'キーワード一覧'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="21" min="1" max="1"/>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D90" s="35" t="inlineStr">
         <is>
-          <t>旧AWS SSO。複数アカウントへのシングルサインオンを一元管理</t>
+          <t>旧AWS SSO。複数のAWSアカウントや外部のSaaSアプリへのシングルサインオンを一元管理</t>
         </is>
       </c>
       <c r="E90" s="35" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D100" s="35" t="inlineStr">
         <is>
-          <t>複数アカウントのWAF・Shield・SGルールを一元管理</t>
+          <t>複数アカウントのWAF・Shield・セキュリティグループ・Network Firewallのルールを一元管理し一括適用</t>
         </is>
       </c>
       <c r="E100" s="37" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D101" s="37" t="inlineStr">
         <is>
-          <t>VPC向けのマネージドネットワークファイアウォール</t>
+          <t>VPC向けのマネージドネットワークファイアウォール。ステートフルなパケット検査やドメイン名によるフィルタリングが可能</t>
         </is>
       </c>
       <c r="E101" s="37" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D105" s="35" t="inlineStr">
         <is>
-          <t>セキュリティアラートとコンプライアンス状況を一元集約</t>
+          <t>複数アカウントのセキュリティアラートを一元集約し、CIS・PCI DSSなど業界標準への準拠状況を自動チェック</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
@@ -5942,15 +5942,108 @@
       </c>
       <c r="G173" s="39" t="n"/>
     </row>
+    <row r="174" ht="29.85" customHeight="1" s="22">
+      <c r="A174" s="34" t="n">
+        <v>170</v>
+      </c>
+      <c r="B174" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C174" s="36" t="inlineStr">
+        <is>
+          <t>AWS Service Catalog</t>
+        </is>
+      </c>
+      <c r="D174" s="35" t="inlineStr">
+        <is>
+          <t>組織で承認したCloudFormationテンプレートなどを「製品」としてカタログ化し、利用者はその中から選んでセルフサービスでデプロイできる</t>
+        </is>
+      </c>
+      <c r="E174" s="37" t="inlineStr">
+        <is>
+          <t>開発者に、承認済みの標準構成のリソースだけをセルフサービスで起動させたい(ガバナンスと標準化)</t>
+        </is>
+      </c>
+      <c r="F174" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G174" s="39" t="n"/>
+    </row>
+    <row r="175" ht="29.85" customHeight="1" s="22">
+      <c r="A175" s="34" t="n">
+        <v>171</v>
+      </c>
+      <c r="B175" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C175" s="36" t="inlineStr">
+        <is>
+          <t>AWS License Manager</t>
+        </is>
+      </c>
+      <c r="D175" s="35" t="inlineStr">
+        <is>
+          <t>Microsoft・Oracleなどのソフトウェアライセンスの利用状況を、AWSとオンプレミスをまたいで一元管理・追跡する。ライセンスルールで上限を超える利用を防げる</t>
+        </is>
+      </c>
+      <c r="E175" s="37" t="inlineStr">
+        <is>
+          <t>BYOLで持ち込んだライセンスの使用数を追跡し、契約数を超える利用を防ぎたい</t>
+        </is>
+      </c>
+      <c r="F175" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G175" s="39" t="n"/>
+    </row>
+    <row r="176" ht="29.85" customHeight="1" s="22">
+      <c r="A176" s="34" t="n">
+        <v>172</v>
+      </c>
+      <c r="B176" s="35" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="C176" s="36" t="inlineStr">
+        <is>
+          <t>AWS Audit Manager</t>
+        </is>
+      </c>
+      <c r="D176" s="35" t="inlineStr">
+        <is>
+          <t>AWSの利用状況から監査の証拠(エビデンス)を継続的に自動収集し、PCI DSS・GDPRなどの規制や業界標準に沿った監査レポートの作成を効率化する</t>
+        </is>
+      </c>
+      <c r="E176" s="37" t="inlineStr">
+        <is>
+          <t>コンプライアンス監査に向けたエビデンス収集を自動化し、監査対応の手間を減らしたい</t>
+        </is>
+      </c>
+      <c r="F176" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G176" s="39" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G173"/>
-  <conditionalFormatting sqref="A5:G173">
+  <autoFilter ref="A4:G176"/>
+  <conditionalFormatting sqref="A5:G176">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>$F5="★★★"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"◎ 説明できる,○ なんとなく,△ 要復習"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5985,6 +6078,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -6029,23 +6123,23 @@
         </is>
       </c>
       <c r="B4" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A4)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A4)</f>
         <v/>
       </c>
       <c r="C4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A4,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G4" s="44">
@@ -6060,23 +6154,23 @@
         </is>
       </c>
       <c r="B5" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A5)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A5)</f>
         <v/>
       </c>
       <c r="C5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A5,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G5" s="44">
@@ -6091,23 +6185,23 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A6)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A6)</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A6,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G6" s="44">
@@ -6122,23 +6216,23 @@
         </is>
       </c>
       <c r="B7" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A7)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A7)</f>
         <v/>
       </c>
       <c r="C7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A7,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G7" s="44">
@@ -6153,23 +6247,23 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A8)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A8)</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A8,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G8" s="44">
@@ -6184,23 +6278,23 @@
         </is>
       </c>
       <c r="B9" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A9)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A9)</f>
         <v/>
       </c>
       <c r="C9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A9,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G9" s="44">
@@ -6215,23 +6309,23 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A10)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A10)</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A10,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G10" s="44">
@@ -6246,23 +6340,23 @@
         </is>
       </c>
       <c r="B11" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A11)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A11)</f>
         <v/>
       </c>
       <c r="C11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A11,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G11" s="44">
@@ -6277,23 +6371,23 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A12)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A12)</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A12,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G12" s="44">
@@ -6308,23 +6402,23 @@
         </is>
       </c>
       <c r="B13" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A13)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A13)</f>
         <v/>
       </c>
       <c r="C13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A13,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G13" s="44">
@@ -6339,23 +6433,23 @@
         </is>
       </c>
       <c r="B14" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A14)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A14)</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A14,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G14" s="44">
@@ -6370,23 +6464,23 @@
         </is>
       </c>
       <c r="B15" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$173,A15)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A15)</f>
         <v/>
       </c>
       <c r="C15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$F$5:$F$173,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$F$5:$F$176,"★★★")</f>
         <v/>
       </c>
       <c r="D15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$G$5:$G$173,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$G$5:$G$176,"◎*")</f>
         <v/>
       </c>
       <c r="E15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$G$5:$G$173,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$G$5:$G$176,"○*")</f>
         <v/>
       </c>
       <c r="F15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$173,A15,キーワード一覧!$G$5:$G$173,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$G$5:$G$176,"△*")</f>
         <v/>
       </c>
       <c r="G15" s="44">
@@ -6425,6 +6519,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="22">
       <c r="A18" s="24" t="inlineStr">
         <is>

--- a/data/AWS_SAA_重要キーワード集.xlsx
+++ b/data/AWS_SAA_重要キーワード集.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分野別集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$203</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'キーワード一覧'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="21" min="1" max="1"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="D131" s="35" t="inlineStr">
         <is>
-          <t>コスト・パフォーマンス・セキュリティ・耐障害性などのベストプラクティスをチェック</t>
+          <t>コスト最適化・パフォーマンス・セキュリティ・耐障害性・サービスの制限・運用上の優秀性の観点で、アカウントの設定をベストプラクティスと照らしてチェックし推奨事項を示す</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D133" s="37" t="inlineStr">
         <is>
-          <t>AWSサービスの障害やメンテナンスの影響を通知</t>
+          <t>AWSサービス全体の稼働状況と、自分のアカウントのリソースに影響するイベント(障害・予定されたメンテナンスなど)を確認・通知</t>
         </is>
       </c>
       <c r="E133" s="35" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="D139" s="35" t="inlineStr">
         <is>
-          <t>コストと使用量の可視化・分析・予測</t>
+          <t>過去のコストと使用量をサービス別・アカウント別などで可視化・分析し、将来のコストも予測</t>
         </is>
       </c>
       <c r="E139" s="35" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D140" s="35" t="inlineStr">
         <is>
-          <t>予算を設定し、超過見込み時にアラート</t>
+          <t>コストや使用量の予算を設定し、実績や予測が閾値を超えたときにアラート(Budgets Actionsで自動対応も可能)</t>
         </is>
       </c>
       <c r="E140" s="35" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D141" s="35" t="inlineStr">
         <is>
-          <t>タグでコストを部門・プロジェクト別に集計</t>
+          <t>リソースに付けたタグ単位でコストを部門・プロジェクト別に集計(タグは請求コンソールで有効化が必要)</t>
         </is>
       </c>
       <c r="E141" s="35" t="inlineStr">
@@ -6035,15 +6035,852 @@
       </c>
       <c r="G176" s="39" t="n"/>
     </row>
+    <row r="177" ht="29.85" customHeight="1" s="22">
+      <c r="A177" s="34" t="n">
+        <v>173</v>
+      </c>
+      <c r="B177" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C177" s="36" t="inlineStr">
+        <is>
+          <t>AWS X-Ray</t>
+        </is>
+      </c>
+      <c r="D177" s="35" t="inlineStr">
+        <is>
+          <t>分散アプリケーションのリクエストをトレース(追跡)し、どのサービスで遅延やエラーが起きているかを特定する</t>
+        </is>
+      </c>
+      <c r="E177" s="37" t="inlineStr">
+        <is>
+          <t>マイクロサービス・サーバーレス構成でボトルネックやエラーの発生箇所を特定したい</t>
+        </is>
+      </c>
+      <c r="F177" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G177" s="39" t="n"/>
+    </row>
+    <row r="178" ht="29.85" customHeight="1" s="22">
+      <c r="A178" s="34" t="n">
+        <v>174</v>
+      </c>
+      <c r="B178" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C178" s="36" t="inlineStr">
+        <is>
+          <t>CloudWatch RUM</t>
+        </is>
+      </c>
+      <c r="D178" s="35" t="inlineStr">
+        <is>
+          <t>実際のユーザーのブラウザ上での体験(ページの表示速度・JavaScriptエラーなど)をリアルタイムに収集・監視する</t>
+        </is>
+      </c>
+      <c r="E178" s="37" t="inlineStr">
+        <is>
+          <t>エンドユーザーの実際の表示性能やクライアント側のエラーを把握したい</t>
+        </is>
+      </c>
+      <c r="F178" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G178" s="39" t="n"/>
+    </row>
+    <row r="179" ht="29.85" customHeight="1" s="22">
+      <c r="A179" s="34" t="n">
+        <v>175</v>
+      </c>
+      <c r="B179" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C179" s="36" t="inlineStr">
+        <is>
+          <t>CloudWatch Application Insights</t>
+        </is>
+      </c>
+      <c r="D179" s="35" t="inlineStr">
+        <is>
+          <t>アプリケーションと基盤リソース(EC2、データベース等)の監視を自動で設定し、問題を検出してダッシュボードで原因の手がかりを示す</t>
+        </is>
+      </c>
+      <c r="E179" s="37" t="inlineStr">
+        <is>
+          <t>.NET・SQL Serverなどのアプリの問題検出と監視設定を自動化したい</t>
+        </is>
+      </c>
+      <c r="F179" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G179" s="39" t="n"/>
+    </row>
+    <row r="180" ht="29.85" customHeight="1" s="22">
+      <c r="A180" s="34" t="n">
+        <v>176</v>
+      </c>
+      <c r="B180" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C180" s="36" t="inlineStr">
+        <is>
+          <t>CloudWatch ServiceLens</t>
+        </is>
+      </c>
+      <c r="D180" s="35" t="inlineStr">
+        <is>
+          <t>X-Rayのトレースと、CloudWatchのメトリクス・ログを統合して、アプリ全体の状態や依存関係を俯瞰する機能。現在はX-Rayのサービスマップと統合され、CloudWatchコンソールの「トレースマップ」になっている</t>
+        </is>
+      </c>
+      <c r="E180" s="37" t="inlineStr">
+        <is>
+          <t>トレース・メトリクス・ログを1か所で関連づけて見たい</t>
+        </is>
+      </c>
+      <c r="F180" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G180" s="39" t="n"/>
+    </row>
+    <row r="181" ht="29.85" customHeight="1" s="22">
+      <c r="A181" s="34" t="n">
+        <v>177</v>
+      </c>
+      <c r="B181" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C181" s="36" t="inlineStr">
+        <is>
+          <t>AWS Well-Architected Tool</t>
+        </is>
+      </c>
+      <c r="D181" s="35" t="inlineStr">
+        <is>
+          <t>6つの柱に沿った質問に回答して、ワークロードの設計をレビューし、ベストプラクティスとの差分(リスク)と改善計画を得られるツール</t>
+        </is>
+      </c>
+      <c r="E181" s="37" t="inlineStr">
+        <is>
+          <t>既存ワークロードの設計をベストプラクティスに照らして定期的にレビューしたい</t>
+        </is>
+      </c>
+      <c r="F181" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G181" s="39" t="n"/>
+    </row>
+    <row r="182" ht="29.85" customHeight="1" s="22">
+      <c r="A182" s="34" t="n">
+        <v>178</v>
+      </c>
+      <c r="B182" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C182" s="36" t="inlineStr">
+        <is>
+          <t>AWS Resource Groups</t>
+        </is>
+      </c>
+      <c r="D182" s="35" t="inlineStr">
+        <is>
+          <t>タグやCloudFormationスタックなどの条件で複数のAWSリソースを論理的にグループ化し、まとめて確認・操作できる</t>
+        </is>
+      </c>
+      <c r="E182" s="37" t="inlineStr">
+        <is>
+          <t>アプリ・環境単位でリソースをまとめて管理し、Systems Managerなどで一括操作したい</t>
+        </is>
+      </c>
+      <c r="F182" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G182" s="39" t="n"/>
+    </row>
+    <row r="183" ht="29.85" customHeight="1" s="22">
+      <c r="A183" s="34" t="n">
+        <v>179</v>
+      </c>
+      <c r="B183" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C183" s="36" t="inlineStr">
+        <is>
+          <t>Tag Editor</t>
+        </is>
+      </c>
+      <c r="D183" s="35" t="inlineStr">
+        <is>
+          <t>複数のリージョン・サービスにまたがるリソースを検索し、タグを一括で追加・編集・削除できるツール</t>
+        </is>
+      </c>
+      <c r="E183" s="37" t="inlineStr">
+        <is>
+          <t>既存の多数のリソースにタグをまとめて付け直したい(コスト配分タグの整備など)</t>
+        </is>
+      </c>
+      <c r="F183" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G183" s="39" t="n"/>
+    </row>
+    <row r="184" ht="29.85" customHeight="1" s="22">
+      <c r="A184" s="34" t="n">
+        <v>180</v>
+      </c>
+      <c r="B184" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C184" s="36" t="inlineStr">
+        <is>
+          <t>AWS Resource Access Manager(RAM)</t>
+        </is>
+      </c>
+      <c r="D184" s="35" t="inlineStr">
+        <is>
+          <t>VPCサブネット・Transit Gateway・Route 53 Resolverルールなどを、ほかのAWSアカウントやOrganizations内で、複製せずに共有できる</t>
+        </is>
+      </c>
+      <c r="E184" s="37" t="inlineStr">
+        <is>
+          <t>複数アカウントで1つのVPCのサブネットやTransit Gatewayを共有したい</t>
+        </is>
+      </c>
+      <c r="F184" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G184" s="39" t="n"/>
+    </row>
+    <row r="185" ht="29.85" customHeight="1" s="22">
+      <c r="A185" s="34" t="n">
+        <v>181</v>
+      </c>
+      <c r="B185" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C185" s="36" t="inlineStr">
+        <is>
+          <t>AWSサポートプラン</t>
+        </is>
+      </c>
+      <c r="D185" s="35" t="inlineStr">
+        <is>
+          <t>AWSの利用を支援するサポート体系。現在は無料のBasicと、有料のBusiness Support+、Enterprise Support、Unified Operationsがあり、上位ほど応答時間が短く支援が手厚い(Developer・Business・Enterprise On-Rampは2027年1月1日に終了)</t>
+        </is>
+      </c>
+      <c r="E185" s="37" t="inlineStr">
+        <is>
+          <t>本番ワークロードの障害対応の速さや、専任担当者が必要かでプランを選ぶ</t>
+        </is>
+      </c>
+      <c r="F185" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G185" s="39" t="n"/>
+    </row>
+    <row r="186" ht="29.85" customHeight="1" s="22">
+      <c r="A186" s="34" t="n">
+        <v>182</v>
+      </c>
+      <c r="B186" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C186" s="36" t="inlineStr">
+        <is>
+          <t>TAM(テクニカルアカウントマネージャー)</t>
+        </is>
+      </c>
+      <c r="D186" s="35" t="inlineStr">
+        <is>
+          <t>自社に指名される技術担当者。アーキテクチャ・運用・コスト・セキュリティなどを事前対応型で支援する。Enterprise SupportとUnified Operationsで利用できる</t>
+        </is>
+      </c>
+      <c r="E186" s="37" t="inlineStr">
+        <is>
+          <t>専任の技術窓口による継続的・プロアクティブな支援が必要→Enterprise Support以上</t>
+        </is>
+      </c>
+      <c r="F186" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G186" s="39" t="n"/>
+    </row>
+    <row r="187" ht="29.85" customHeight="1" s="22">
+      <c r="A187" s="34" t="n">
+        <v>183</v>
+      </c>
+      <c r="B187" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C187" s="36" t="inlineStr">
+        <is>
+          <t>コンシェルジュサポートチーム</t>
+        </is>
+      </c>
+      <c r="D187" s="35" t="inlineStr">
+        <is>
+          <t>請求やアカウント管理など、技術以外の問い合わせに対応する上位プラン向けの専門チーム。請求内容の確認やコストを抑える使い方の見直しも支援する</t>
+        </is>
+      </c>
+      <c r="E187" s="37" t="inlineStr">
+        <is>
+          <t>請求・アカウント管理の手厚い支援が必要→Enterprise Support以上</t>
+        </is>
+      </c>
+      <c r="F187" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G187" s="39" t="n"/>
+    </row>
+    <row r="188" ht="29.85" customHeight="1" s="22">
+      <c r="A188" s="34" t="n">
+        <v>184</v>
+      </c>
+      <c r="B188" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C188" s="36" t="inlineStr">
+        <is>
+          <t>AWSパートナーネットワーク(APN)</t>
+        </is>
+      </c>
+      <c r="D188" s="35" t="inlineStr">
+        <is>
+          <t>AWSを活用したソリューションやサービスを提供するパートナー企業のプログラム・コミュニティ。AWSの技術支援などを受けながら顧客のAWS導入を支援する</t>
+        </is>
+      </c>
+      <c r="E188" s="37" t="inlineStr">
+        <is>
+          <t>自社にスキルがなく、導入・移行を支援する外部企業を探したい</t>
+        </is>
+      </c>
+      <c r="F188" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G188" s="39" t="n"/>
+    </row>
+    <row r="189" ht="29.85" customHeight="1" s="22">
+      <c r="A189" s="34" t="n">
+        <v>185</v>
+      </c>
+      <c r="B189" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C189" s="36" t="inlineStr">
+        <is>
+          <t>AWSプロフェッショナルサービス</t>
+        </is>
+      </c>
+      <c r="D189" s="35" t="inlineStr">
+        <is>
+          <t>AWSのエキスパートチームが、クラウド導入や移行などで企業の目標に沿った成果を出せるよう支援する、AWS直営のコンサルティングサービス</t>
+        </is>
+      </c>
+      <c r="E189" s="37" t="inlineStr">
+        <is>
+          <t>大規模な移行・変革をAWS自身の専門チームに支援してほしい</t>
+        </is>
+      </c>
+      <c r="F189" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G189" s="39" t="n"/>
+    </row>
+    <row r="190" ht="29.85" customHeight="1" s="22">
+      <c r="A190" s="34" t="n">
+        <v>186</v>
+      </c>
+      <c r="B190" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C190" s="36" t="inlineStr">
+        <is>
+          <t>AWSパートナーパス</t>
+        </is>
+      </c>
+      <c r="D190" s="35" t="inlineStr">
+        <is>
+          <t>APNの現在の参加の枠組み。ソフトウェア・サービス・トレーニングなどのパス(道筋)ごとに、トレーニング・技術支援・マーケティング支援などの特典を受けられる</t>
+        </is>
+      </c>
+      <c r="E190" s="37" t="inlineStr">
+        <is>
+          <t>パートナー企業がAWSとの協業を深めるためのプログラム</t>
+        </is>
+      </c>
+      <c r="F190" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G190" s="39" t="n"/>
+    </row>
+    <row r="191" ht="29.85" customHeight="1" s="22">
+      <c r="A191" s="34" t="n">
+        <v>187</v>
+      </c>
+      <c r="B191" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C191" s="36" t="inlineStr">
+        <is>
+          <t>コンサルティングパートナー</t>
+        </is>
+      </c>
+      <c r="D191" s="35" t="inlineStr">
+        <is>
+          <t>AWS上のシステムの設計・構築・移行・運用などを顧客に代わって行うパートナー企業(SIerなど)。パートナーパスでは「サービス」パスにあたる</t>
+        </is>
+      </c>
+      <c r="E191" s="37" t="inlineStr">
+        <is>
+          <t>設計・構築・移行を任せられる外部の企業を探したい</t>
+        </is>
+      </c>
+      <c r="F191" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G191" s="39" t="n"/>
+    </row>
+    <row r="192" ht="29.85" customHeight="1" s="22">
+      <c r="A192" s="34" t="n">
+        <v>188</v>
+      </c>
+      <c r="B192" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C192" s="36" t="inlineStr">
+        <is>
+          <t>AWS IQ</t>
+        </is>
+      </c>
+      <c r="D192" s="35" t="inlineStr">
+        <is>
+          <t>AWS認定の専門家(個人・企業)を探し、プロジェクト単位で依頼・協働できたマーケットプレイス。2026年5月28日にサービス終了し、AWS Marketplaceのプロフェッショナルサービスなどに移行している</t>
+        </is>
+      </c>
+      <c r="E192" s="37" t="inlineStr">
+        <is>
+          <t>試験ではほぼ出題されない。外部の専門家への依頼はAPNのパートナーやAWS Marketplaceで探す</t>
+        </is>
+      </c>
+      <c r="F192" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G192" s="39" t="n"/>
+    </row>
+    <row r="193" ht="29.85" customHeight="1" s="22">
+      <c r="A193" s="34" t="n">
+        <v>189</v>
+      </c>
+      <c r="B193" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C193" s="36" t="inlineStr">
+        <is>
+          <t>AWS Managed Services(AMS)</t>
+        </is>
+      </c>
+      <c r="D193" s="35" t="inlineStr">
+        <is>
+          <t>AWSインフラの運用(監視、パッチ適用、インシデント対応、変更管理、バックアップなど)をAWSに任せられるサービス</t>
+        </is>
+      </c>
+      <c r="E193" s="37" t="inlineStr">
+        <is>
+          <t>運用の人手が足りず、インフラ運用そのものをAWSに委託したい</t>
+        </is>
+      </c>
+      <c r="F193" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G193" s="39" t="n"/>
+    </row>
+    <row r="194" ht="29.85" customHeight="1" s="22">
+      <c r="A194" s="34" t="n">
+        <v>190</v>
+      </c>
+      <c r="B194" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C194" s="36" t="inlineStr">
+        <is>
+          <t>Service Quotas</t>
+        </is>
+      </c>
+      <c r="D194" s="35" t="inlineStr">
+        <is>
+          <t>AWSサービスごとの利用上限(クォータ)を一元的に確認し、引き上げを申請できる。CloudWatchで上限への接近をアラームできる</t>
+        </is>
+      </c>
+      <c r="E194" s="37" t="inlineStr">
+        <is>
+          <t>上限に達してリソースを作れない事態を防ぐ。クォータの確認と引き上げ申請</t>
+        </is>
+      </c>
+      <c r="F194" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G194" s="39" t="n"/>
+    </row>
+    <row r="195" ht="29.85" customHeight="1" s="22">
+      <c r="A195" s="34" t="n">
+        <v>191</v>
+      </c>
+      <c r="B195" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C195" s="36" t="inlineStr">
+        <is>
+          <t>AWS Partner Solutions(旧クイックスタート)</t>
+        </is>
+      </c>
+      <c r="D195" s="35" t="inlineStr">
+        <is>
+          <t>AWSやパートナーが作成した、ベストプラクティスに沿った構成をCloudFormationテンプレートで短時間にデプロイできるリファレンス構成集</t>
+        </is>
+      </c>
+      <c r="E195" s="37" t="inlineStr">
+        <is>
+          <t>定番の構成をベストプラクティスに沿ってすばやく自動構築したい</t>
+        </is>
+      </c>
+      <c r="F195" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G195" s="39" t="n"/>
+    </row>
+    <row r="196" ht="29.85" customHeight="1" s="22">
+      <c r="A196" s="34" t="n">
+        <v>192</v>
+      </c>
+      <c r="B196" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C196" s="36" t="inlineStr">
+        <is>
+          <t>AWS Artifact</t>
+        </is>
+      </c>
+      <c r="D196" s="35" t="inlineStr">
+        <is>
+          <t>AWSのコンプライアンスレポート(SOC、ISO、PCIなど)や契約・合意書(BAAなど)をオンラインでダウンロードできるセルフサービスのポータル</t>
+        </is>
+      </c>
+      <c r="E196" s="37" t="inlineStr">
+        <is>
+          <t>監査人にAWS側のコンプライアンスの証明書・レポートを提出したい</t>
+        </is>
+      </c>
+      <c r="F196" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G196" s="39" t="n"/>
+    </row>
+    <row r="197" ht="29.85" customHeight="1" s="22">
+      <c r="A197" s="34" t="n">
+        <v>193</v>
+      </c>
+      <c r="B197" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C197" s="36" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana</t>
+        </is>
+      </c>
+      <c r="D197" s="35" t="inlineStr">
+        <is>
+          <t>オープンソースの可視化ツールGrafanaをフルマネージドで提供し、複数のデータソースのメトリクス・ログ・トレースをダッシュボードで可視化する</t>
+        </is>
+      </c>
+      <c r="E197" s="37" t="inlineStr">
+        <is>
+          <t>CloudWatch・Prometheusなど複数のデータソースを1つのダッシュボードで可視化したい</t>
+        </is>
+      </c>
+      <c r="F197" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G197" s="39" t="n"/>
+    </row>
+    <row r="198" ht="29.85" customHeight="1" s="22">
+      <c r="A198" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="B198" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C198" s="36" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="D198" s="35" t="inlineStr">
+        <is>
+          <t>Prometheus互換のメトリクス監視をマネージドで提供し、EKS・ECSなどのコンテナ環境のメトリクスを収集・保存・クエリできる</t>
+        </is>
+      </c>
+      <c r="E198" s="37" t="inlineStr">
+        <is>
+          <t>コンテナのメトリクス監視を、Prometheusのまま運用負荷なく拡張したい</t>
+        </is>
+      </c>
+      <c r="F198" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G198" s="39" t="n"/>
+    </row>
+    <row r="199" ht="29.85" customHeight="1" s="22">
+      <c r="A199" s="34" t="n">
+        <v>195</v>
+      </c>
+      <c r="B199" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C199" s="36" t="inlineStr">
+        <is>
+          <t>AWS Proton</t>
+        </is>
+      </c>
+      <c r="D199" s="35" t="inlineStr">
+        <is>
+          <t>プラットフォームチームがコンテナやサーバーレス向けのインフラテンプレートを標準化し、開発者がセルフサービスでデプロイできるようにするサービス。2026年10月7日にサポート終了</t>
+        </is>
+      </c>
+      <c r="E199" s="37" t="inlineStr">
+        <is>
+          <t>試験ではほぼ出題されない。標準構成のセルフサービス提供はService Catalogなどを選ぶ</t>
+        </is>
+      </c>
+      <c r="F199" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G199" s="39" t="n"/>
+    </row>
+    <row r="200" ht="29.85" customHeight="1" s="22">
+      <c r="A200" s="34" t="n">
+        <v>196</v>
+      </c>
+      <c r="B200" s="35" t="inlineStr">
+        <is>
+          <t>コスト管理</t>
+        </is>
+      </c>
+      <c r="C200" s="36" t="inlineStr">
+        <is>
+          <t>AWS Cost and Usage Report(CUR)</t>
+        </is>
+      </c>
+      <c r="D200" s="35" t="inlineStr">
+        <is>
+          <t>AWSの利用料金と使用量について最も詳細なデータを、CSV/Parquet形式でS3に出力するレポート。Athenaなどで詳細に分析できる</t>
+        </is>
+      </c>
+      <c r="E200" s="37" t="inlineStr">
+        <is>
+          <t>リソース単位・時間単位の詳細なコストデータをSQLで分析したい</t>
+        </is>
+      </c>
+      <c r="F200" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G200" s="39" t="n"/>
+    </row>
+    <row r="201" ht="29.85" customHeight="1" s="22">
+      <c r="A201" s="34" t="n">
+        <v>197</v>
+      </c>
+      <c r="B201" s="35" t="inlineStr">
+        <is>
+          <t>コスト管理</t>
+        </is>
+      </c>
+      <c r="C201" s="36" t="inlineStr">
+        <is>
+          <t>コストカテゴリ</t>
+        </is>
+      </c>
+      <c r="D201" s="35" t="inlineStr">
+        <is>
+          <t>アカウント・タグ・サービスなどのルールで、コストを独自のグループ(部門・プロジェクトなど)に分類する機能。Cost ExplorerやBudgetsで使える</t>
+        </is>
+      </c>
+      <c r="E201" s="37" t="inlineStr">
+        <is>
+          <t>複数の条件を組み合わせて、組織の単位ごとにコストを集計したい</t>
+        </is>
+      </c>
+      <c r="F201" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G201" s="39" t="n"/>
+    </row>
+    <row r="202" ht="29.85" customHeight="1" s="22">
+      <c r="A202" s="34" t="n">
+        <v>198</v>
+      </c>
+      <c r="B202" s="35" t="inlineStr">
+        <is>
+          <t>コスト管理</t>
+        </is>
+      </c>
+      <c r="C202" s="36" t="inlineStr">
+        <is>
+          <t>AWS Pricing Calculator</t>
+        </is>
+      </c>
+      <c r="D202" s="35" t="inlineStr">
+        <is>
+          <t>これから使うAWSサービスの構成を入力して、事前に月額コストを見積もれるツール</t>
+        </is>
+      </c>
+      <c r="E202" s="37" t="inlineStr">
+        <is>
+          <t>移行・構築前のコスト見積もり</t>
+        </is>
+      </c>
+      <c r="F202" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G202" s="39" t="n"/>
+    </row>
+    <row r="203" ht="29.85" customHeight="1" s="22">
+      <c r="A203" s="34" t="n">
+        <v>199</v>
+      </c>
+      <c r="B203" s="35" t="inlineStr">
+        <is>
+          <t>コスト管理</t>
+        </is>
+      </c>
+      <c r="C203" s="36" t="inlineStr">
+        <is>
+          <t>AWS Cost Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="D203" s="35" t="inlineStr">
+        <is>
+          <t>機械学習でコストの異常(急な増加など)を自動で検出し、原因の手がかりとともに通知する</t>
+        </is>
+      </c>
+      <c r="E203" s="37" t="inlineStr">
+        <is>
+          <t>固定の予算額ではなく、いつもと違うコストの増え方を検知したい</t>
+        </is>
+      </c>
+      <c r="F203" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G203" s="39" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G176"/>
-  <conditionalFormatting sqref="A5:G176">
+  <autoFilter ref="A4:G203"/>
+  <conditionalFormatting sqref="A5:G203">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>$F5="★★★"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"◎ 説明できる,○ なんとなく,△ 要復習"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6078,7 +6915,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -6123,23 +6959,23 @@
         </is>
       </c>
       <c r="B4" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A4)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A4)</f>
         <v/>
       </c>
       <c r="C4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A4,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G4" s="44">
@@ -6154,23 +6990,23 @@
         </is>
       </c>
       <c r="B5" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A5)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A5)</f>
         <v/>
       </c>
       <c r="C5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A5,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G5" s="44">
@@ -6185,23 +7021,23 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A6)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A6)</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A6,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G6" s="44">
@@ -6216,23 +7052,23 @@
         </is>
       </c>
       <c r="B7" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A7)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A7)</f>
         <v/>
       </c>
       <c r="C7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A7,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G7" s="44">
@@ -6247,23 +7083,23 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A8)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A8)</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A8,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G8" s="44">
@@ -6278,23 +7114,23 @@
         </is>
       </c>
       <c r="B9" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A9)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A9)</f>
         <v/>
       </c>
       <c r="C9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A9,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G9" s="44">
@@ -6309,23 +7145,23 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A10)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A10)</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A10,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G10" s="44">
@@ -6340,23 +7176,23 @@
         </is>
       </c>
       <c r="B11" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A11)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A11)</f>
         <v/>
       </c>
       <c r="C11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A11,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G11" s="44">
@@ -6371,23 +7207,23 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A12)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A12)</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A12,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G12" s="44">
@@ -6402,23 +7238,23 @@
         </is>
       </c>
       <c r="B13" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A13)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A13)</f>
         <v/>
       </c>
       <c r="C13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A13,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G13" s="44">
@@ -6433,23 +7269,23 @@
         </is>
       </c>
       <c r="B14" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A14)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A14)</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A14,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G14" s="44">
@@ -6464,23 +7300,23 @@
         </is>
       </c>
       <c r="B15" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$176,A15)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A15)</f>
         <v/>
       </c>
       <c r="C15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$F$5:$F$176,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$F$5:$F$203,"★★★")</f>
         <v/>
       </c>
       <c r="D15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$G$5:$G$176,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$G$5:$G$203,"◎*")</f>
         <v/>
       </c>
       <c r="E15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$G$5:$G$176,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$G$5:$G$203,"○*")</f>
         <v/>
       </c>
       <c r="F15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$176,A15,キーワード一覧!$G$5:$G$176,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$G$5:$G$203,"△*")</f>
         <v/>
       </c>
       <c r="G15" s="44">
@@ -6519,7 +7355,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="22">
       <c r="A18" s="24" t="inlineStr">
         <is>

--- a/data/AWS_SAA_重要キーワード集.xlsx
+++ b/data/AWS_SAA_重要キーワード集.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分野別集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$212</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'キーワード一覧'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="21" min="1" max="1"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>複数サービス(EBS、RDS、DynamoDB、EFS等)のバックアップを一元管理</t>
+          <t>複数サービス(EC2、EBS、RDS、DynamoDB、EFS等)のバックアップを一元管理。バックアッププランで取得スケジュール・保持期間を自動化</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D107" s="35" t="inlineStr">
         <is>
-          <t>フルマネージドのメッセージキュー。標準キュー(少なくとも1回・順序保証なし)とFIFOキュー(順序保証・1回のみ)</t>
+          <t>フルマネージドのメッセージキュー。コンシューマーがポーリングして取り出す(Pull型)。標準キュー(少なくとも1回・順序保証なし)とFIFOキュー(順序保証・1回のみ)</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D110" s="37" t="inlineStr">
         <is>
-          <t>Pub/Sub型の通知サービス。メール・SMS・SQS・Lambda・HTTPへ配信</t>
+          <t>Pub/Sub型の通知サービス。1つのメッセージを購読先(メール・SMS・SQS・Lambda・HTTP)へ一斉にプッシュ配信(Push型)</t>
         </is>
       </c>
       <c r="E110" s="35" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="E114" s="35" t="inlineStr">
         <is>
-          <t>既存のMQTT・AMQP等の標準プロトコルを使うアプリの移行</t>
+          <t>既存のMQTT・AMQP等の標準プロトコルを使うアプリを、コード変更を最小限にして移行</t>
         </is>
       </c>
       <c r="F114" s="38" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D115" s="35" t="inlineStr">
         <is>
-          <t>マネージドGraphQL API</t>
+          <t>マネージドGraphQL API。リアルタイム更新(サブスクリプション)やオフライン同期に対応</t>
         </is>
       </c>
       <c r="E115" s="37" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="D135" s="37" t="inlineStr">
         <is>
-          <t>Database Migration Service。最小限のダウンタイムでDBを移行(同種・異種)</t>
+          <t>Database Migration Service。移行中もソースDBを稼働させたまま、DBをAWSへ移行・継続的にレプリケーションする。同種(Oracle→Oracle)・異種(Oracle→Aurora)のどちらにも対応</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D136" s="37" t="inlineStr">
         <is>
-          <t>Schema Conversion Tool。異種DB間のスキーマ変換</t>
+          <t>Schema Conversion Tool。異種DB間でスキーマやコード(ストアドプロシージャ等)を変換する。同じ変換エンジンをマネージドで使えるDMS Schema Conversionもある</t>
         </is>
       </c>
       <c r="E136" s="37" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D137" s="35" t="inlineStr">
         <is>
-          <t>サーバーをそのままAWSへリホスト(リフト&amp;シフト)</t>
+          <t>サーバーをそのままAWS(EC2)へリホスト(リフト&amp;シフト)する。ブロックレベルで継続的にレプリケートし、切り替え時のダウンタイムを最小化する</t>
         </is>
       </c>
       <c r="E137" s="35" t="inlineStr">
@@ -6872,15 +6872,294 @@
       </c>
       <c r="G203" s="39" t="n"/>
     </row>
+    <row r="204" ht="29.85" customHeight="1" s="22">
+      <c r="A204" s="34" t="n">
+        <v>200</v>
+      </c>
+      <c r="B204" s="35" t="inlineStr">
+        <is>
+          <t>移行</t>
+        </is>
+      </c>
+      <c r="C204" s="36" t="inlineStr">
+        <is>
+          <t>VM Import/Export</t>
+        </is>
+      </c>
+      <c r="D204" s="35" t="inlineStr">
+        <is>
+          <t>VMware vSphere・Microsoft Hyper-Vなどの仮想マシンイメージをインポートしてEC2のAMIにする、またはEC2インスタンスを仮想マシンイメージとしてエクスポートする機能</t>
+        </is>
+      </c>
+      <c r="E204" s="37" t="inlineStr">
+        <is>
+          <t>既存の仮想マシンイメージ(社内で作り込んだゴールデンイメージなど)をそのままEC2で使いたい</t>
+        </is>
+      </c>
+      <c r="F204" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G204" s="39" t="n"/>
+    </row>
+    <row r="205" ht="29.85" customHeight="1" s="22">
+      <c r="A205" s="34" t="n">
+        <v>201</v>
+      </c>
+      <c r="B205" s="35" t="inlineStr">
+        <is>
+          <t>移行</t>
+        </is>
+      </c>
+      <c r="C205" s="36" t="inlineStr">
+        <is>
+          <t>AWS Application Discovery Service</t>
+        </is>
+      </c>
+      <c r="D205" s="35" t="inlineStr">
+        <is>
+          <t>オンプレミスのサーバーの構成情報・使用状況(CPU・メモリ・ディスク)・サーバー間の通信(依存関係)を収集して、移行計画に役立てる。エージェント型とエージェントレス型がある。2025年11月7日から新規の利用は受け付けておらず、AWS Transformが後継として案内されている</t>
+        </is>
+      </c>
+      <c r="E205" s="37" t="inlineStr">
+        <is>
+          <t>移行前にオンプレミスのサーバー一覧・使用率・依存関係を把握したい</t>
+        </is>
+      </c>
+      <c r="F205" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G205" s="39" t="n"/>
+    </row>
+    <row r="206" ht="29.85" customHeight="1" s="22">
+      <c r="A206" s="34" t="n">
+        <v>202</v>
+      </c>
+      <c r="B206" s="35" t="inlineStr">
+        <is>
+          <t>移行</t>
+        </is>
+      </c>
+      <c r="C206" s="36" t="inlineStr">
+        <is>
+          <t>AWS Migration Hub</t>
+        </is>
+      </c>
+      <c r="D206" s="35" t="inlineStr">
+        <is>
+          <t>Application Migration ServiceやDMSなど、複数の移行ツールによる移行の進捗を1か所で追跡・管理する。2025年11月7日から新規の利用は受け付けておらず、AWS Transformが後継として案内されている</t>
+        </is>
+      </c>
+      <c r="E206" s="37" t="inlineStr">
+        <is>
+          <t>複数のツール・アカウントにまたがる移行の状況を一元的に把握したい</t>
+        </is>
+      </c>
+      <c r="F206" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G206" s="39" t="n"/>
+    </row>
+    <row r="207" ht="29.85" customHeight="1" s="22">
+      <c r="A207" s="34" t="n">
+        <v>203</v>
+      </c>
+      <c r="B207" s="35" t="inlineStr">
+        <is>
+          <t>移行</t>
+        </is>
+      </c>
+      <c r="C207" s="36" t="inlineStr">
+        <is>
+          <t>Migration Evaluator</t>
+        </is>
+      </c>
+      <c r="D207" s="35" t="inlineStr">
+        <is>
+          <t>オンプレミス環境の使用状況を収集・分析し、AWSへ移行した後のコストを見積もって、移行の費用対効果(ビジネスケース)の作成を支援する(旧TSO Logic)</t>
+        </is>
+      </c>
+      <c r="E207" s="37" t="inlineStr">
+        <is>
+          <t>移行するかどうかを判断するため、現状とAWS移行後のコストを比較したい</t>
+        </is>
+      </c>
+      <c r="F207" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G207" s="39" t="n"/>
+    </row>
+    <row r="208" ht="29.85" customHeight="1" s="22">
+      <c r="A208" s="34" t="n">
+        <v>204</v>
+      </c>
+      <c r="B208" s="35" t="inlineStr">
+        <is>
+          <t>ストレージ</t>
+        </is>
+      </c>
+      <c r="C208" s="36" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="D208" s="35" t="inlineStr">
+        <is>
+          <t>SFTP・FTPS・FTP(およびAS2)で、S3やEFSに直接ファイルを転送できるフルマネージドのファイル転送サービス</t>
+        </is>
+      </c>
+      <c r="E208" s="37" t="inlineStr">
+        <is>
+          <t>取引先が使っている既存のSFTP/FTPの手順を変えずに、ファイルの保存先をS3にしたい</t>
+        </is>
+      </c>
+      <c r="F208" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G208" s="39" t="n"/>
+    </row>
+    <row r="209" ht="29.85" customHeight="1" s="22">
+      <c r="A209" s="34" t="n">
+        <v>205</v>
+      </c>
+      <c r="B209" s="35" t="inlineStr">
+        <is>
+          <t>コンピューティング</t>
+        </is>
+      </c>
+      <c r="C209" s="36" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="D209" s="35" t="inlineStr">
+        <is>
+          <t>AWSが提供・管理するハードウェア(ラック・サーバー)を自社データセンターに設置し、EC2・EBS・RDSなどをAWSと同じAPI・ツールでオンプレミスで利用できるハイブリッドサービス</t>
+        </is>
+      </c>
+      <c r="E209" s="37" t="inlineStr">
+        <is>
+          <t>データをオンプレミスに置く必要がある・オンプレミスのシステムと超低レイテンシで連携したいが、AWSと同じ運用をしたい</t>
+        </is>
+      </c>
+      <c r="F209" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G209" s="39" t="n"/>
+    </row>
+    <row r="210" ht="29.85" customHeight="1" s="22">
+      <c r="A210" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="B210" s="35" t="inlineStr">
+        <is>
+          <t>移行</t>
+        </is>
+      </c>
+      <c r="C210" s="36" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery(DRS)</t>
+        </is>
+      </c>
+      <c r="D210" s="35" t="inlineStr">
+        <is>
+          <t>オンプレミスや他のクラウド、AWS上のサーバーをブロックレベルで継続的にAWSへレプリケートし、災害時に数分でAWS上に復旧(フェイルオーバー)できる。平常時は低コストなステージング環境だけを維持する(旧CloudEndure Disaster Recovery)</t>
+        </is>
+      </c>
+      <c r="E210" s="37" t="inlineStr">
+        <is>
+          <t>サーバーのDRを低コストで、秒単位のRPO・分単位のRTOで実現したい</t>
+        </is>
+      </c>
+      <c r="F210" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G210" s="39" t="n"/>
+    </row>
+    <row r="211" ht="29.85" customHeight="1" s="22">
+      <c r="A211" s="34" t="n">
+        <v>207</v>
+      </c>
+      <c r="B211" s="35" t="inlineStr">
+        <is>
+          <t>アプリケーション統合</t>
+        </is>
+      </c>
+      <c r="C211" s="36" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="D211" s="35" t="inlineStr">
+        <is>
+          <t>Simple Email Service。アプリケーションからメールを大量に送信(および受信)できるサービス。通知メール・マーケティングメールなどに使う</t>
+        </is>
+      </c>
+      <c r="E211" s="37" t="inlineStr">
+        <is>
+          <t>アプリから顧客へのメールを大量に送りたい(件名・本文を自由に作れる。SNSのメール通知は運用者向けの簡易な通知)</t>
+        </is>
+      </c>
+      <c r="F211" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G211" s="39" t="n"/>
+    </row>
+    <row r="212" ht="29.85" customHeight="1" s="22">
+      <c r="A212" s="34" t="n">
+        <v>208</v>
+      </c>
+      <c r="B212" s="35" t="inlineStr">
+        <is>
+          <t>アプリケーション統合</t>
+        </is>
+      </c>
+      <c r="C212" s="36" t="inlineStr">
+        <is>
+          <t>Amazon AppFlow</t>
+        </is>
+      </c>
+      <c r="D212" s="35" t="inlineStr">
+        <is>
+          <t>Salesforce・SAP・Slack・ZendeskなどのSaaSとS3・Redshiftなどの間で、コードを書かずにデータを双方向に転送できる。スケジュール・イベントでの実行やフィルタ・変換にも対応</t>
+        </is>
+      </c>
+      <c r="E212" s="37" t="inlineStr">
+        <is>
+          <t>SaaSのデータを定期的にS3やRedshiftへ取り込みたい(コード不要)</t>
+        </is>
+      </c>
+      <c r="F212" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G212" s="39" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G203"/>
-  <conditionalFormatting sqref="A5:G203">
+  <autoFilter ref="A4:G212"/>
+  <conditionalFormatting sqref="A5:G212">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>$F5="★★★"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"◎ 説明できる,○ なんとなく,△ 要復習"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6915,6 +7194,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -6959,23 +7239,23 @@
         </is>
       </c>
       <c r="B4" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A4)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A4)</f>
         <v/>
       </c>
       <c r="C4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A4,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G4" s="44">
@@ -6990,23 +7270,23 @@
         </is>
       </c>
       <c r="B5" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A5)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A5)</f>
         <v/>
       </c>
       <c r="C5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A5,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G5" s="44">
@@ -7021,23 +7301,23 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A6)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A6)</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A6,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G6" s="44">
@@ -7052,23 +7332,23 @@
         </is>
       </c>
       <c r="B7" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A7)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A7)</f>
         <v/>
       </c>
       <c r="C7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A7,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G7" s="44">
@@ -7083,23 +7363,23 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A8)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A8)</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A8,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G8" s="44">
@@ -7114,23 +7394,23 @@
         </is>
       </c>
       <c r="B9" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A9)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A9)</f>
         <v/>
       </c>
       <c r="C9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A9,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G9" s="44">
@@ -7145,23 +7425,23 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A10)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A10)</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A10,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G10" s="44">
@@ -7176,23 +7456,23 @@
         </is>
       </c>
       <c r="B11" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A11)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A11)</f>
         <v/>
       </c>
       <c r="C11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A11,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G11" s="44">
@@ -7207,23 +7487,23 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A12)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A12)</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A12,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G12" s="44">
@@ -7238,23 +7518,23 @@
         </is>
       </c>
       <c r="B13" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A13)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A13)</f>
         <v/>
       </c>
       <c r="C13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A13,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G13" s="44">
@@ -7269,23 +7549,23 @@
         </is>
       </c>
       <c r="B14" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A14)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A14)</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A14,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G14" s="44">
@@ -7300,23 +7580,23 @@
         </is>
       </c>
       <c r="B15" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$203,A15)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A15)</f>
         <v/>
       </c>
       <c r="C15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$F$5:$F$203,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$F$5:$F$212,"★★★")</f>
         <v/>
       </c>
       <c r="D15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$G$5:$G$203,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$G$5:$G$212,"◎*")</f>
         <v/>
       </c>
       <c r="E15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$G$5:$G$203,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$G$5:$G$212,"○*")</f>
         <v/>
       </c>
       <c r="F15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$203,A15,キーワード一覧!$G$5:$G$203,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$G$5:$G$212,"△*")</f>
         <v/>
       </c>
       <c r="G15" s="44">
@@ -7355,6 +7635,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="22">
       <c r="A18" s="24" t="inlineStr">
         <is>

--- a/data/AWS_SAA_重要キーワード集.xlsx
+++ b/data/AWS_SAA_重要キーワード集.xlsx
@@ -11,7 +11,7 @@
     <sheet name="分野別集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'キーワード一覧'!$A$4:$G$235</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'キーワード一覧'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="21" min="1" max="1"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D17" s="37" t="inlineStr">
         <is>
-          <t>AWS独自のコンテナオーケストレーション。起動タイプはEC2またはFargate</t>
+          <t>AWS独自のコンテナオーケストレーション。コンテナの起動・停止・配置・スケーリングを管理する。起動タイプはEC2またはFargate</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>マネージドKubernetes</t>
+          <t>マネージドKubernetes。コントロールプレーンの運用をAWSに任せられ、既存のKubernetesのツールをそのまま使える</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="D116" s="35" t="inlineStr">
         <is>
-          <t>リアルタイムのストリーミングデータ収集。シャード単位でスケール</t>
+          <t>リアルタイムのストリーミングデータ(ログ・クリックストリーム・IoTなど)を収集・保持し、複数のコンシューマーで処理できる。シャード単位で容量を設計し、データはデフォルト24時間・最大365日保持</t>
         </is>
       </c>
       <c r="E116" s="35" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D117" s="35" t="inlineStr">
         <is>
-          <t>旧Kinesis Data Firehose。ストリーミングデータをS3・Redshift・OpenSearch等へ自動配信(ほぼリアルタイム)</t>
+          <t>旧Kinesis Data Firehose。ストリーミングデータをS3・Redshift・OpenSearch等へ自動配信(ほぼリアルタイム)。シャード管理が不要で、Lambdaによる変換も可能</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D119" s="35" t="inlineStr">
         <is>
-          <t>サーバーレスETLとデータカタログ</t>
+          <t>サーバーレスETLとデータカタログ。クローラーがデータのスキーマを自動検出してカタログに登録する</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D120" s="37" t="inlineStr">
         <is>
-          <t>S3上のデータレイクの構築とアクセス権限の一元管理</t>
+          <t>S3上のデータレイクの構築とアクセス権限の一元管理。データベース・テーブル・列・行単位のきめ細かいアクセス制御ができる</t>
         </is>
       </c>
       <c r="E120" s="35" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D121" s="37" t="inlineStr">
         <is>
-          <t>Hadoop・Sparkなどのビッグデータ処理クラスター</t>
+          <t>Hadoop・Spark・Hiveなどのビッグデータ処理フレームワークをマネージドのクラスターで実行</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="D123" s="35" t="inlineStr">
         <is>
-          <t>サーバーレスのBI・ダッシュボード</t>
+          <t>サーバーレスのBIサービス。各種データソースのデータをダッシュボード・グラフで可視化・共有</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="D124" s="35" t="inlineStr">
         <is>
-          <t>マネージドApache Kafka</t>
+          <t>Managed Streaming for Apache Kafka。Apache Kafkaをフルマネージドで提供</t>
         </is>
       </c>
       <c r="E124" s="35" t="inlineStr">
         <is>
-          <t>既存Kafkaアプリの移行</t>
+          <t>既存Kafkaアプリをほぼそのまま移行</t>
         </is>
       </c>
       <c r="F124" s="38" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D130" s="35" t="inlineStr">
         <is>
-          <t>インフラをコード(YAML/JSON)で定義し自動構築(IaC)</t>
+          <t>インフラをコード(YAML/JSON)のテンプレートで定義し、スタック単位で作成・更新・削除を自動化(IaC)。変更セットで更新前に差分を確認できる</t>
         </is>
       </c>
       <c r="E130" s="35" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="D211" s="35" t="inlineStr">
         <is>
-          <t>Simple Email Service。アプリケーションからメールを大量に送信(および受信)できるサービス。通知メール・マーケティングメールなどに使う</t>
+          <t>Simple Email Service。アプリケーションからメールを大量に送信(および受信)できるサービス。通知メール・マーケティングメールなどに使う。SPF・DKIM・DMARCによる送信ドメイン認証で到達率を高められる</t>
         </is>
       </c>
       <c r="E211" s="37" t="inlineStr">
@@ -7151,15 +7151,728 @@
       </c>
       <c r="G212" s="39" t="n"/>
     </row>
+    <row r="213" ht="29.85" customHeight="1" s="22">
+      <c r="A213" s="34" t="n">
+        <v>209</v>
+      </c>
+      <c r="B213" s="35" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="C213" s="36" t="inlineStr">
+        <is>
+          <t>AWS Data Exchange</t>
+        </is>
+      </c>
+      <c r="D213" s="35" t="inlineStr">
+        <is>
+          <t>サードパーティが提供するデータセット(金融・気象・人口統計など)を検索・購読し、AWS上でそのまま利用できるデータ取引サービス</t>
+        </is>
+      </c>
+      <c r="E213" s="37" t="inlineStr">
+        <is>
+          <t>外部の商用データを購読してS3などに取り込みたい</t>
+        </is>
+      </c>
+      <c r="F213" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G213" s="39" t="n"/>
+    </row>
+    <row r="214" ht="29.85" customHeight="1" s="22">
+      <c r="A214" s="34" t="n">
+        <v>210</v>
+      </c>
+      <c r="B214" s="35" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="C214" s="36" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Apache Flink</t>
+        </is>
+      </c>
+      <c r="D214" s="35" t="inlineStr">
+        <is>
+          <t>旧Kinesis Data Analytics。Apache Flinkでストリーミングデータをリアルタイムに分析・加工する。SQL・Java・Pythonなどで処理を記述できる</t>
+        </is>
+      </c>
+      <c r="E214" s="37" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams・MSKのデータをリアルタイムに集計・異常検知したい</t>
+        </is>
+      </c>
+      <c r="F214" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G214" s="39" t="n"/>
+    </row>
+    <row r="215" ht="29.85" customHeight="1" s="22">
+      <c r="A215" s="34" t="n">
+        <v>211</v>
+      </c>
+      <c r="B215" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C215" s="36" t="inlineStr">
+        <is>
+          <t>AWS CDK</t>
+        </is>
+      </c>
+      <c r="D215" s="35" t="inlineStr">
+        <is>
+          <t>Cloud Development Kit。Python・TypeScript・Javaなどのプログラミング言語でインフラを定義できるフレームワーク。CloudFormationテンプレートに変換されてデプロイされる</t>
+        </is>
+      </c>
+      <c r="E215" s="37" t="inlineStr">
+        <is>
+          <t>使い慣れたプログラミング言語でIaCを書きたい</t>
+        </is>
+      </c>
+      <c r="F215" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G215" s="39" t="n"/>
+    </row>
+    <row r="216" ht="29.85" customHeight="1" s="22">
+      <c r="A216" s="34" t="n">
+        <v>212</v>
+      </c>
+      <c r="B216" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C216" s="36" t="inlineStr">
+        <is>
+          <t>AWS SAM</t>
+        </is>
+      </c>
+      <c r="D216" s="35" t="inlineStr">
+        <is>
+          <t>Serverless Application Model。Lambda・API Gateway・DynamoDBなどのサーバーレスアプリを簡潔なテンプレートで定義・ビルド・デプロイできる。CloudFormationの拡張で、ローカルでのテストも可能</t>
+        </is>
+      </c>
+      <c r="E216" s="37" t="inlineStr">
+        <is>
+          <t>サーバーレスアプリを簡潔に定義してデプロイしたい</t>
+        </is>
+      </c>
+      <c r="F216" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G216" s="39" t="n"/>
+    </row>
+    <row r="217" ht="29.85" customHeight="1" s="22">
+      <c r="A217" s="34" t="n">
+        <v>213</v>
+      </c>
+      <c r="B217" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C217" s="36" t="inlineStr">
+        <is>
+          <t>AWS Launch Wizard</t>
+        </is>
+      </c>
+      <c r="D217" s="35" t="inlineStr">
+        <is>
+          <t>SQL Server・SAPなどの商用アプリケーションを、ガイドに沿って要件を入力するだけでベストプラクティスに沿った構成でデプロイできる</t>
+        </is>
+      </c>
+      <c r="E217" s="37" t="inlineStr">
+        <is>
+          <t>SQL ServerやSAPの環境をベストプラクティス通りに素早く構築したい</t>
+        </is>
+      </c>
+      <c r="F217" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G217" s="39" t="n"/>
+    </row>
+    <row r="218" ht="29.85" customHeight="1" s="22">
+      <c r="A218" s="34" t="n">
+        <v>214</v>
+      </c>
+      <c r="B218" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C218" s="36" t="inlineStr">
+        <is>
+          <t>AWS CodeCommit</t>
+        </is>
+      </c>
+      <c r="D218" s="35" t="inlineStr">
+        <is>
+          <t>フルマネージドのプライベートGitリポジトリ。2024年に新規受付を停止したが、2025年11月に新規受付を再開した</t>
+        </is>
+      </c>
+      <c r="E218" s="37" t="inlineStr">
+        <is>
+          <t>AWS上でソースコードをGitで安全に管理したい</t>
+        </is>
+      </c>
+      <c r="F218" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G218" s="39" t="n"/>
+    </row>
+    <row r="219" ht="29.85" customHeight="1" s="22">
+      <c r="A219" s="34" t="n">
+        <v>215</v>
+      </c>
+      <c r="B219" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C219" s="36" t="inlineStr">
+        <is>
+          <t>AWS CodeBuild</t>
+        </is>
+      </c>
+      <c r="D219" s="35" t="inlineStr">
+        <is>
+          <t>ソースコードのコンパイル・テスト実行・成果物(アーティファクト)の作成を行うフルマネージドのビルドサービス。ビルドサーバーの管理が不要で、使った分だけの従量課金</t>
+        </is>
+      </c>
+      <c r="E219" s="37" t="inlineStr">
+        <is>
+          <t>ビルドサーバーを持たずにビルド・テストを自動化したい</t>
+        </is>
+      </c>
+      <c r="F219" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G219" s="39" t="n"/>
+    </row>
+    <row r="220" ht="29.85" customHeight="1" s="22">
+      <c r="A220" s="34" t="n">
+        <v>216</v>
+      </c>
+      <c r="B220" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C220" s="36" t="inlineStr">
+        <is>
+          <t>AWS CodeDeploy</t>
+        </is>
+      </c>
+      <c r="D220" s="35" t="inlineStr">
+        <is>
+          <t>EC2・オンプレミスサーバー・Lambda・ECSへのアプリケーションのデプロイを自動化する。インプレース方式・Blue/Green方式に対応し、失敗時は自動ロールバックできる</t>
+        </is>
+      </c>
+      <c r="E220" s="37" t="inlineStr">
+        <is>
+          <t>デプロイの自動化。Blue/Greenデプロイで停止時間を減らす</t>
+        </is>
+      </c>
+      <c r="F220" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G220" s="39" t="n"/>
+    </row>
+    <row r="221" ht="29.85" customHeight="1" s="22">
+      <c r="A221" s="34" t="n">
+        <v>217</v>
+      </c>
+      <c r="B221" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C221" s="36" t="inlineStr">
+        <is>
+          <t>AWS CodePipeline</t>
+        </is>
+      </c>
+      <c r="D221" s="35" t="inlineStr">
+        <is>
+          <t>ソース取得→ビルド→テスト→デプロイの一連のリリース工程を自動化するCI/CDパイプライン。CodeCommit・CodeBuild・CodeDeployなどを連携させる</t>
+        </is>
+      </c>
+      <c r="E221" s="37" t="inlineStr">
+        <is>
+          <t>コードの変更から本番デプロイまでのリリース工程を自動化したい</t>
+        </is>
+      </c>
+      <c r="F221" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G221" s="39" t="n"/>
+    </row>
+    <row r="222" ht="29.85" customHeight="1" s="22">
+      <c r="A222" s="34" t="n">
+        <v>218</v>
+      </c>
+      <c r="B222" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C222" s="36" t="inlineStr">
+        <is>
+          <t>AWS Toolkit(IDE Toolkits)</t>
+        </is>
+      </c>
+      <c r="D222" s="35" t="inlineStr">
+        <is>
+          <t>VS Code・JetBrains・Visual StudioなどのIDEに追加する拡張機能。IDE上からAWSリソースの操作や、Lambdaなどのデバッグ・デプロイができる</t>
+        </is>
+      </c>
+      <c r="E222" s="37" t="inlineStr">
+        <is>
+          <t>IDEから離れずにAWSリソースを操作・デプロイしたい</t>
+        </is>
+      </c>
+      <c r="F222" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G222" s="39" t="n"/>
+    </row>
+    <row r="223" ht="29.85" customHeight="1" s="22">
+      <c r="A223" s="34" t="n">
+        <v>219</v>
+      </c>
+      <c r="B223" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C223" s="36" t="inlineStr">
+        <is>
+          <t>Amazon Q Developer</t>
+        </is>
+      </c>
+      <c r="D223" s="35" t="inlineStr">
+        <is>
+          <t>生成AIを活用した開発支援アシスタント。コードの生成・補完・解説、デバッグ、セキュリティ脆弱性のスキャン、AWSに関する質問への回答をIDEやコンソールで行える</t>
+        </is>
+      </c>
+      <c r="E223" s="37" t="inlineStr">
+        <is>
+          <t>生成AIでコーディングやAWSの運用作業を支援したい</t>
+        </is>
+      </c>
+      <c r="F223" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G223" s="39" t="n"/>
+    </row>
+    <row r="224" ht="29.85" customHeight="1" s="22">
+      <c r="A224" s="34" t="n">
+        <v>220</v>
+      </c>
+      <c r="B224" s="35" t="inlineStr">
+        <is>
+          <t>コンピューティング</t>
+        </is>
+      </c>
+      <c r="C224" s="36" t="inlineStr">
+        <is>
+          <t>Amazon ECR</t>
+        </is>
+      </c>
+      <c r="D224" s="35" t="inlineStr">
+        <is>
+          <t>Elastic Container Registry。コンテナイメージを保存・管理・配布するフルマネージドのレジストリ。イメージの脆弱性スキャンやIAMによるアクセス制御に対応</t>
+        </is>
+      </c>
+      <c r="E224" s="37" t="inlineStr">
+        <is>
+          <t>ECS・EKSで使うコンテナイメージの保管場所</t>
+        </is>
+      </c>
+      <c r="F224" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G224" s="39" t="n"/>
+    </row>
+    <row r="225" ht="29.85" customHeight="1" s="22">
+      <c r="A225" s="34" t="n">
+        <v>221</v>
+      </c>
+      <c r="B225" s="35" t="inlineStr">
+        <is>
+          <t>コンピューティング</t>
+        </is>
+      </c>
+      <c r="C225" s="36" t="inlineStr">
+        <is>
+          <t>Amazon ECS Anywhere</t>
+        </is>
+      </c>
+      <c r="D225" s="35" t="inlineStr">
+        <is>
+          <t>ECSの管理機能を使って、オンプレミスのサーバーや仮想マシン上でもコンテナを実行・管理できる機能</t>
+        </is>
+      </c>
+      <c r="E225" s="37" t="inlineStr">
+        <is>
+          <t>オンプレミスのコンテナもECSで一元管理したい</t>
+        </is>
+      </c>
+      <c r="F225" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G225" s="39" t="n"/>
+    </row>
+    <row r="226" ht="29.85" customHeight="1" s="22">
+      <c r="A226" s="34" t="n">
+        <v>222</v>
+      </c>
+      <c r="B226" s="35" t="inlineStr">
+        <is>
+          <t>コンピューティング</t>
+        </is>
+      </c>
+      <c r="C226" s="36" t="inlineStr">
+        <is>
+          <t>Amazon EKS Anywhere</t>
+        </is>
+      </c>
+      <c r="D226" s="35" t="inlineStr">
+        <is>
+          <t>オンプレミス環境にKubernetesクラスターを構築・運用できるサービス。EKSと同じ操作感でオンプレミスでも利用できる</t>
+        </is>
+      </c>
+      <c r="E226" s="37" t="inlineStr">
+        <is>
+          <t>オンプレミスでもEKSと同じ方法でKubernetesを運用したい</t>
+        </is>
+      </c>
+      <c r="F226" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G226" s="39" t="n"/>
+    </row>
+    <row r="227" ht="29.85" customHeight="1" s="22">
+      <c r="A227" s="34" t="n">
+        <v>223</v>
+      </c>
+      <c r="B227" s="35" t="inlineStr">
+        <is>
+          <t>コンピューティング</t>
+        </is>
+      </c>
+      <c r="C227" s="36" t="inlineStr">
+        <is>
+          <t>Amazon EKS Distro(EKS-D)</t>
+        </is>
+      </c>
+      <c r="D227" s="35" t="inlineStr">
+        <is>
+          <t>AWSがEKSで使用しているKubernetesのディストリビューション(オープンソース)。自分の環境で同じバージョンのKubernetesを動かせる</t>
+        </is>
+      </c>
+      <c r="E227" s="37" t="inlineStr">
+        <is>
+          <t>EKSと同じKubernetesを自前の環境で使いたい</t>
+        </is>
+      </c>
+      <c r="F227" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G227" s="39" t="n"/>
+    </row>
+    <row r="228" ht="29.85" customHeight="1" s="22">
+      <c r="A228" s="34" t="n">
+        <v>224</v>
+      </c>
+      <c r="B228" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C228" s="36" t="inlineStr">
+        <is>
+          <t>Amazon CodeGuru</t>
+        </is>
+      </c>
+      <c r="D228" s="35" t="inlineStr">
+        <is>
+          <t>機械学習でコードをレビューし、バグ・セキュリティ上の問題・パフォーマンスの改善点を提案する。Reviewer(コードレビュー)とProfiler(実行時のパフォーマンス分析)で構成。Reviewerは2025年11月7日から新規のリポジトリ関連付けを停止(既存のみ利用可)</t>
+        </is>
+      </c>
+      <c r="E228" s="37" t="inlineStr">
+        <is>
+          <t>コードの品質やアプリの性能のボトルネックを機械学習で見つけたい</t>
+        </is>
+      </c>
+      <c r="F228" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G228" s="39" t="n"/>
+    </row>
+    <row r="229" ht="29.85" customHeight="1" s="22">
+      <c r="A229" s="34" t="n">
+        <v>225</v>
+      </c>
+      <c r="B229" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C229" s="36" t="inlineStr">
+        <is>
+          <t>AWS Fault Injection Service(FIS)</t>
+        </is>
+      </c>
+      <c r="D229" s="35" t="inlineStr">
+        <is>
+          <t>旧Fault Injection Simulator。EC2の停止やネットワーク遅延などの障害を意図的に発生させ、システムの耐障害性を検証するカオスエンジニアリングのサービス</t>
+        </is>
+      </c>
+      <c r="E229" s="37" t="inlineStr">
+        <is>
+          <t>障害を意図的に起こして耐障害性を本番前に検証したい</t>
+        </is>
+      </c>
+      <c r="F229" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G229" s="39" t="n"/>
+    </row>
+    <row r="230" ht="29.85" customHeight="1" s="22">
+      <c r="A230" s="34" t="n">
+        <v>226</v>
+      </c>
+      <c r="B230" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C230" s="36" t="inlineStr">
+        <is>
+          <t>AWS CodeArtifact</t>
+        </is>
+      </c>
+      <c r="D230" s="35" t="inlineStr">
+        <is>
+          <t>npm・Maven・pip・NuGetなどのソフトウェアパッケージを保存・共有できるマネージドのアーティファクトリポジトリ。外部の公開リポジトリとも連携できる</t>
+        </is>
+      </c>
+      <c r="E230" s="37" t="inlineStr">
+        <is>
+          <t>社内で使う依存ライブラリを一元管理したい</t>
+        </is>
+      </c>
+      <c r="F230" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G230" s="39" t="n"/>
+    </row>
+    <row r="231" ht="29.85" customHeight="1" s="22">
+      <c r="A231" s="34" t="n">
+        <v>227</v>
+      </c>
+      <c r="B231" s="35" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="C231" s="36" t="inlineStr">
+        <is>
+          <t>AWS Signer</t>
+        </is>
+      </c>
+      <c r="D231" s="35" t="inlineStr">
+        <is>
+          <t>コードにデジタル署名を付けるサービス。Lambda関数のコードやコンテナイメージが改ざんされていない、信頼できるものであることを保証できる</t>
+        </is>
+      </c>
+      <c r="E231" s="37" t="inlineStr">
+        <is>
+          <t>署名済みのコードだけをLambdaにデプロイさせたい</t>
+        </is>
+      </c>
+      <c r="F231" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G231" s="39" t="n"/>
+    </row>
+    <row r="232" ht="29.85" customHeight="1" s="22">
+      <c r="A232" s="34" t="n">
+        <v>228</v>
+      </c>
+      <c r="B232" s="35" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="C232" s="36" t="inlineStr">
+        <is>
+          <t>AWS Encryption SDK</t>
+        </is>
+      </c>
+      <c r="D232" s="35" t="inlineStr">
+        <is>
+          <t>アプリケーション内でクライアント側の暗号化・復号を行うためのライブラリ。KMSなどと連携して鍵を管理し、エンベロープ暗号化を簡単に実装できる</t>
+        </is>
+      </c>
+      <c r="E232" s="37" t="inlineStr">
+        <is>
+          <t>データをAWSに送る前にアプリ側で暗号化したい</t>
+        </is>
+      </c>
+      <c r="F232" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G232" s="39" t="n"/>
+    </row>
+    <row r="233" ht="29.85" customHeight="1" s="22">
+      <c r="A233" s="34" t="n">
+        <v>229</v>
+      </c>
+      <c r="B233" s="35" t="inlineStr">
+        <is>
+          <t>管理・監視</t>
+        </is>
+      </c>
+      <c r="C233" s="36" t="inlineStr">
+        <is>
+          <t>AWS Device Farm</t>
+        </is>
+      </c>
+      <c r="D233" s="35" t="inlineStr">
+        <is>
+          <t>iOS・Androidの実機やデスクトップブラウザでアプリやWebサイトを自動・手動でテストできる。多数のデバイスで並行してテストし、動画やログで結果を確認できる</t>
+        </is>
+      </c>
+      <c r="E233" s="37" t="inlineStr">
+        <is>
+          <t>多数の実機でモバイルアプリのテストを自動化したい</t>
+        </is>
+      </c>
+      <c r="F233" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G233" s="39" t="n"/>
+    </row>
+    <row r="234" ht="29.85" customHeight="1" s="22">
+      <c r="A234" s="34" t="n">
+        <v>230</v>
+      </c>
+      <c r="B234" s="35" t="inlineStr">
+        <is>
+          <t>アプリケーション統合</t>
+        </is>
+      </c>
+      <c r="C234" s="36" t="inlineStr">
+        <is>
+          <t>Amazon Pinpoint</t>
+        </is>
+      </c>
+      <c r="D234" s="35" t="inlineStr">
+        <is>
+          <t>メール・SMS・プッシュ通知などで、ユーザーの属性・行動のセグメントに応じたマーケティング施策を実施・分析するサービス。2025年5月20日に新規受付を停止し、2026年10月30日でサポート終了(SMS・プッシュ通知などはAWS End User Messaging、メールはSESへ移行)</t>
+        </is>
+      </c>
+      <c r="E234" s="37" t="inlineStr">
+        <is>
+          <t>セグメント別のマーケティングメッセージ配信と効果分析</t>
+        </is>
+      </c>
+      <c r="F234" s="38" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G234" s="39" t="n"/>
+    </row>
+    <row r="235" ht="29.85" customHeight="1" s="22">
+      <c r="A235" s="34" t="n">
+        <v>231</v>
+      </c>
+      <c r="B235" s="35" t="inlineStr">
+        <is>
+          <t>設計原則</t>
+        </is>
+      </c>
+      <c r="C235" s="36" t="inlineStr">
+        <is>
+          <t>IaC(Infrastructure as Code)</t>
+        </is>
+      </c>
+      <c r="D235" s="35" t="inlineStr">
+        <is>
+          <t>インフラの構成をコードで定義して自動構築する考え方。同じ環境を何度でも再現でき、バージョン管理・レビュー・ロールバックが容易になり、手作業のミスを減らせる</t>
+        </is>
+      </c>
+      <c r="E235" s="37" t="inlineStr">
+        <is>
+          <t>開発・検証・本番の環境差異をなくし、同じ構成を繰り返し構築したい</t>
+        </is>
+      </c>
+      <c r="F235" s="38" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G235" s="39" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G212"/>
-  <conditionalFormatting sqref="A5:G212">
+  <autoFilter ref="A4:G235"/>
+  <conditionalFormatting sqref="A5:G235">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>$F5="★★★"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G235" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"◎ 説明できる,○ なんとなく,△ 要復習"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7239,23 +7952,23 @@
         </is>
       </c>
       <c r="B4" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A4)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A4)</f>
         <v/>
       </c>
       <c r="C4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A4,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A4,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A4,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F4" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A4,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A4,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G4" s="44">
@@ -7270,23 +7983,23 @@
         </is>
       </c>
       <c r="B5" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A5)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A5)</f>
         <v/>
       </c>
       <c r="C5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A5,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A5,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A5,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A5,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A5,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G5" s="44">
@@ -7301,23 +8014,23 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A6)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A6)</f>
         <v/>
       </c>
       <c r="C6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A6,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A6,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A6,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F6" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A6,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A6,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G6" s="44">
@@ -7332,23 +8045,23 @@
         </is>
       </c>
       <c r="B7" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A7)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A7)</f>
         <v/>
       </c>
       <c r="C7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A7,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A7,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A7,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A7,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A7,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G7" s="44">
@@ -7363,23 +8076,23 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A8)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A8)</f>
         <v/>
       </c>
       <c r="C8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A8,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A8,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A8,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F8" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A8,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A8,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G8" s="44">
@@ -7394,23 +8107,23 @@
         </is>
       </c>
       <c r="B9" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A9)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A9)</f>
         <v/>
       </c>
       <c r="C9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A9,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A9,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A9,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A9,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A9,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G9" s="44">
@@ -7425,23 +8138,23 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A10)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A10)</f>
         <v/>
       </c>
       <c r="C10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A10,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A10,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A10,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F10" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A10,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A10,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G10" s="44">
@@ -7456,23 +8169,23 @@
         </is>
       </c>
       <c r="B11" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A11)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A11)</f>
         <v/>
       </c>
       <c r="C11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A11,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A11,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A11,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A11,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A11,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G11" s="44">
@@ -7487,23 +8200,23 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A12)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A12)</f>
         <v/>
       </c>
       <c r="C12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A12,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A12,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A12,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F12" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A12,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A12,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G12" s="44">
@@ -7518,23 +8231,23 @@
         </is>
       </c>
       <c r="B13" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A13)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A13)</f>
         <v/>
       </c>
       <c r="C13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A13,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A13,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A13,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A13,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A13,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G13" s="44">
@@ -7549,23 +8262,23 @@
         </is>
       </c>
       <c r="B14" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A14)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A14)</f>
         <v/>
       </c>
       <c r="C14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A14,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A14,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A14,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F14" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A14,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A14,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G14" s="44">
@@ -7580,23 +8293,23 @@
         </is>
       </c>
       <c r="B15" s="43">
-        <f>COUNTIF(キーワード一覧!$B$5:$B$212,A15)</f>
+        <f>COUNTIF(キーワード一覧!$B$5:$B$235,A15)</f>
         <v/>
       </c>
       <c r="C15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$F$5:$F$212,"★★★")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A15,キーワード一覧!$F$5:$F$235,"★★★")</f>
         <v/>
       </c>
       <c r="D15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$G$5:$G$212,"◎*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A15,キーワード一覧!$G$5:$G$235,"◎*")</f>
         <v/>
       </c>
       <c r="E15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$G$5:$G$212,"○*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A15,キーワード一覧!$G$5:$G$235,"○*")</f>
         <v/>
       </c>
       <c r="F15" s="43">
-        <f>COUNTIFS(キーワード一覧!$B$5:$B$212,A15,キーワード一覧!$G$5:$G$212,"△*")</f>
+        <f>COUNTIFS(キーワード一覧!$B$5:$B$235,A15,キーワード一覧!$G$5:$G$235,"△*")</f>
         <v/>
       </c>
       <c r="G15" s="44">
